--- a/tests/fixtures/korea-sample.xlsx
+++ b/tests/fixtures/korea-sample.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,12 +597,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0805100000</t>
+          <t>1006100000</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -632,11 +632,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FIN1</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FCEPA1</t>
+          <t>FIN1</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -692,7 +692,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FID1</t>
+          <t>FCEPA1</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -717,16 +717,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1006301000</t>
+          <t>0805100000</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>FID1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1006302000</t>
+          <t>1006301000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8544491100</t>
+          <t>1006302000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8544491800</t>
+          <t>8544491100</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -837,7 +837,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6109100000</t>
+          <t>8544491800</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -855,40 +855,135 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>20200101</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20201231</t>
+          <t>20261231</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>6109100000</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>20200101</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20201231</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>2903430000</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>6.5</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0803900000</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2401103000</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>40</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>20261231</t>
         </is>
@@ -905,7 +1000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1084,12 +1179,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0805100000</t>
+          <t>1006100000</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1119,11 +1214,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FIN1</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1149,7 +1244,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FCEPA1</t>
+          <t>FIN1</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1179,7 +1274,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FID1</t>
+          <t>FCEPA1</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1204,16 +1299,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1006301000</t>
+          <t>0805100000</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>FID1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1329,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1006302000</t>
+          <t>1006301000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1243,7 +1338,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1264,7 +1359,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8544491100</t>
+          <t>1006302000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1273,7 +1368,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1294,7 +1389,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8544491800</t>
+          <t>8544491100</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1324,7 +1419,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6109100000</t>
+          <t>8544491800</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1333,7 +1428,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1342,40 +1437,165 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>20200101</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20201231</t>
+          <t>20261231</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>6109100000</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>20200101</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20201231</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>2903430000</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>6.5</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0803900000</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0803900000</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>20260212</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2401103000</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>40</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>20261231</t>
         </is>
